--- a/research/traditional_assets/database/data/switzerland/switzerland_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0119</v>
+        <v>0.0329</v>
       </c>
       <c r="E2">
-        <v>0.0503</v>
+        <v>0.0611</v>
       </c>
       <c r="F2">
-        <v>0.109</v>
+        <v>0.0785</v>
       </c>
       <c r="G2">
-        <v>0.08119880749648684</v>
+        <v>0.08484913377733044</v>
       </c>
       <c r="H2">
-        <v>0.08119880749648684</v>
+        <v>0.08484913377733044</v>
       </c>
       <c r="I2">
-        <v>0.08693805898602179</v>
+        <v>0.07292973852710025</v>
       </c>
       <c r="J2">
-        <v>0.0674661798932179</v>
+        <v>0.0549543583857243</v>
       </c>
       <c r="K2">
-        <v>1217.9</v>
+        <v>1330</v>
       </c>
       <c r="L2">
-        <v>0.05331681456220149</v>
+        <v>0.05696297406685654</v>
       </c>
       <c r="M2">
-        <v>1307.7</v>
+        <v>1224.2</v>
       </c>
       <c r="N2">
-        <v>0.06830361340060796</v>
+        <v>0.07701696109517339</v>
       </c>
       <c r="O2">
-        <v>1.073733475654815</v>
+        <v>0.9204511278195489</v>
       </c>
       <c r="P2">
-        <v>707.4</v>
+        <v>800.1</v>
       </c>
       <c r="Q2">
-        <v>0.03694882321602055</v>
+        <v>0.05033595047561528</v>
       </c>
       <c r="R2">
-        <v>0.5808358650135479</v>
+        <v>0.6015789473684211</v>
       </c>
       <c r="S2">
-        <v>600.2999999999998</v>
+        <v>424.1</v>
       </c>
       <c r="T2">
-        <v>0.4590502408809359</v>
+        <v>0.3464303218428361</v>
       </c>
       <c r="U2">
-        <v>9366.799999999999</v>
+        <v>6085.6</v>
       </c>
       <c r="V2">
-        <v>0.4892454584391028</v>
+        <v>0.3828577180532488</v>
       </c>
       <c r="W2">
-        <v>0.07389945693395225</v>
+        <v>0.07525774362572571</v>
       </c>
       <c r="X2">
-        <v>0.06473635241520662</v>
+        <v>0.1272157391947054</v>
       </c>
       <c r="Y2">
-        <v>0.009163104518745635</v>
+        <v>-0.05195799556897968</v>
       </c>
       <c r="Z2">
-        <v>1.969894531687924</v>
+        <v>1.92255753633332</v>
       </c>
       <c r="AA2">
-        <v>0.1329012588455237</v>
+        <v>0.1056529158688364</v>
       </c>
       <c r="AB2">
-        <v>0.05559688354883199</v>
+        <v>0.08511649710579475</v>
       </c>
       <c r="AC2">
-        <v>0.07730437529669174</v>
+        <v>0.02053641876304167</v>
       </c>
       <c r="AD2">
-        <v>5501.1</v>
+        <v>16722.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5501.1</v>
+        <v>16722.5</v>
       </c>
       <c r="AG2">
-        <v>-3865.699999999999</v>
+        <v>10636.9</v>
       </c>
       <c r="AH2">
-        <v>0.2232000486884548</v>
+        <v>0.5126817648086774</v>
       </c>
       <c r="AI2">
-        <v>0.2362934263427373</v>
+        <v>0.5946898437750047</v>
       </c>
       <c r="AJ2">
-        <v>-0.2529958048914572</v>
+        <v>0.4009068260710611</v>
       </c>
       <c r="AK2">
-        <v>-0.2778280868190311</v>
+        <v>0.4827471963910485</v>
       </c>
       <c r="AL2">
-        <v>302.9</v>
+        <v>285.9</v>
       </c>
       <c r="AM2">
-        <v>302.9</v>
+        <v>285.9</v>
       </c>
       <c r="AN2">
-        <v>2.716860924535757</v>
+        <v>9.596292895673132</v>
       </c>
       <c r="AO2">
-        <v>6.556289204357875</v>
+        <v>5.955928646379854</v>
       </c>
       <c r="AP2">
-        <v>-1.909176214934808</v>
+        <v>6.104039940319064</v>
       </c>
       <c r="AQ2">
-        <v>6.556289204357875</v>
+        <v>5.955928646379854</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0119</v>
+        <v>0.0329</v>
       </c>
       <c r="E3">
-        <v>0.0503</v>
+        <v>0.0611</v>
       </c>
       <c r="F3">
-        <v>0.109</v>
+        <v>0.0785</v>
       </c>
       <c r="G3">
-        <v>0.08119880749648684</v>
+        <v>0.08484913377733044</v>
       </c>
       <c r="H3">
-        <v>0.08119880749648684</v>
+        <v>0.08484913377733044</v>
       </c>
       <c r="I3">
-        <v>0.08693805898602179</v>
+        <v>0.07292973852710025</v>
       </c>
       <c r="J3">
-        <v>0.0674661798932179</v>
+        <v>0.0549543583857243</v>
       </c>
       <c r="K3">
-        <v>1217.9</v>
+        <v>1330</v>
       </c>
       <c r="L3">
-        <v>0.05331681456220149</v>
+        <v>0.05696297406685654</v>
       </c>
       <c r="M3">
-        <v>1307.7</v>
+        <v>1224.2</v>
       </c>
       <c r="N3">
-        <v>0.06830361340060796</v>
+        <v>0.07701696109517339</v>
       </c>
       <c r="O3">
-        <v>1.073733475654815</v>
+        <v>0.9204511278195489</v>
       </c>
       <c r="P3">
-        <v>707.4</v>
+        <v>800.1</v>
       </c>
       <c r="Q3">
-        <v>0.03694882321602055</v>
+        <v>0.05033595047561528</v>
       </c>
       <c r="R3">
-        <v>0.5808358650135479</v>
+        <v>0.6015789473684211</v>
       </c>
       <c r="S3">
-        <v>600.2999999999998</v>
+        <v>424.1</v>
       </c>
       <c r="T3">
-        <v>0.4590502408809359</v>
+        <v>0.3464303218428361</v>
       </c>
       <c r="U3">
-        <v>9366.799999999999</v>
+        <v>6085.6</v>
       </c>
       <c r="V3">
-        <v>0.4892454584391028</v>
+        <v>0.3828577180532488</v>
       </c>
       <c r="W3">
-        <v>0.07389945693395225</v>
+        <v>0.07525774362572571</v>
       </c>
       <c r="X3">
-        <v>0.06473635241520662</v>
+        <v>0.1272157391947054</v>
       </c>
       <c r="Y3">
-        <v>0.009163104518745635</v>
+        <v>-0.05195799556897968</v>
       </c>
       <c r="Z3">
-        <v>1.969894531687924</v>
+        <v>1.92255753633332</v>
       </c>
       <c r="AA3">
-        <v>0.1329012588455237</v>
+        <v>0.1056529158688364</v>
       </c>
       <c r="AB3">
-        <v>0.05559688354883199</v>
+        <v>0.08511649710579475</v>
       </c>
       <c r="AC3">
-        <v>0.07730437529669174</v>
+        <v>0.02053641876304167</v>
       </c>
       <c r="AD3">
-        <v>5501.1</v>
+        <v>16722.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5501.1</v>
+        <v>16722.5</v>
       </c>
       <c r="AG3">
-        <v>-3865.699999999999</v>
+        <v>10636.9</v>
       </c>
       <c r="AH3">
-        <v>0.2232000486884548</v>
+        <v>0.5126817648086774</v>
       </c>
       <c r="AI3">
-        <v>0.2362934263427373</v>
+        <v>0.5946898437750047</v>
       </c>
       <c r="AJ3">
-        <v>-0.2529958048914572</v>
+        <v>0.4009068260710611</v>
       </c>
       <c r="AK3">
-        <v>-0.2778280868190311</v>
+        <v>0.4827471963910485</v>
       </c>
       <c r="AL3">
-        <v>302.9</v>
+        <v>285.9</v>
       </c>
       <c r="AM3">
-        <v>302.9</v>
+        <v>285.9</v>
       </c>
       <c r="AN3">
-        <v>2.716860924535757</v>
+        <v>9.596292895673132</v>
       </c>
       <c r="AO3">
-        <v>6.556289204357875</v>
+        <v>5.955928646379854</v>
       </c>
       <c r="AP3">
-        <v>-1.909176214934808</v>
+        <v>6.104039940319064</v>
       </c>
       <c r="AQ3">
-        <v>6.556289204357875</v>
+        <v>5.955928646379854</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0329</v>
+        <v>0.0194</v>
       </c>
       <c r="E2">
-        <v>0.0611</v>
+        <v>0.0549</v>
       </c>
       <c r="F2">
-        <v>0.0785</v>
+        <v>0.106</v>
       </c>
       <c r="G2">
-        <v>0.08484913377733044</v>
+        <v>0.09297391789636097</v>
       </c>
       <c r="H2">
-        <v>0.08484913377733044</v>
+        <v>0.09297391789636097</v>
       </c>
       <c r="I2">
-        <v>0.07292973852710025</v>
+        <v>0.08955977217142951</v>
       </c>
       <c r="J2">
-        <v>0.0549543583857243</v>
+        <v>0.06992661717638164</v>
       </c>
       <c r="K2">
-        <v>1330</v>
+        <v>1524.3</v>
       </c>
       <c r="L2">
-        <v>0.05696297406685654</v>
+        <v>0.06255026837155098</v>
       </c>
       <c r="M2">
-        <v>1224.2</v>
+        <v>1689.6</v>
       </c>
       <c r="N2">
-        <v>0.07701696109517339</v>
+        <v>0.08621991794411217</v>
       </c>
       <c r="O2">
-        <v>0.9204511278195489</v>
+        <v>1.108443219838614</v>
       </c>
       <c r="P2">
-        <v>800.1</v>
+        <v>980</v>
       </c>
       <c r="Q2">
-        <v>0.05033595047561528</v>
+        <v>0.05000918536057643</v>
       </c>
       <c r="R2">
-        <v>0.6015789473684211</v>
+        <v>0.6429180607491963</v>
       </c>
       <c r="S2">
-        <v>424.1</v>
+        <v>709.5999999999999</v>
       </c>
       <c r="T2">
-        <v>0.3464303218428361</v>
+        <v>0.4199810606060606</v>
       </c>
       <c r="U2">
-        <v>6085.6</v>
+        <v>5426.5</v>
       </c>
       <c r="V2">
-        <v>0.3828577180532488</v>
+        <v>0.2769131064889469</v>
       </c>
       <c r="W2">
-        <v>0.07525774362572571</v>
+        <v>0.1352588846000266</v>
       </c>
       <c r="X2">
-        <v>0.1272157391947054</v>
+        <v>0.1029892905569705</v>
       </c>
       <c r="Y2">
-        <v>-0.05195799556897968</v>
+        <v>0.03226959404305607</v>
       </c>
       <c r="Z2">
-        <v>1.92255753633332</v>
+        <v>1.200583314447871</v>
       </c>
       <c r="AA2">
-        <v>0.1056529158688364</v>
+        <v>0.08395272981774771</v>
       </c>
       <c r="AB2">
-        <v>0.08511649710579475</v>
+        <v>0.07432040677157861</v>
       </c>
       <c r="AC2">
-        <v>0.02053641876304167</v>
+        <v>0.009632323046169095</v>
       </c>
       <c r="AD2">
-        <v>16722.5</v>
+        <v>18187.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>16722.5</v>
+        <v>18187.2</v>
       </c>
       <c r="AG2">
-        <v>10636.9</v>
+        <v>12760.7</v>
       </c>
       <c r="AH2">
-        <v>0.5126817648086774</v>
+        <v>0.4813516975619051</v>
       </c>
       <c r="AI2">
-        <v>0.5946898437750047</v>
+        <v>0.655668675914977</v>
       </c>
       <c r="AJ2">
-        <v>0.4009068260710611</v>
+        <v>0.3943709417716668</v>
       </c>
       <c r="AK2">
-        <v>0.4827471963910485</v>
+        <v>0.5719235027048346</v>
       </c>
       <c r="AL2">
-        <v>285.9</v>
+        <v>488.3</v>
       </c>
       <c r="AM2">
-        <v>285.9</v>
+        <v>488.3</v>
       </c>
       <c r="AN2">
-        <v>9.596292895673132</v>
+        <v>8.081045054652094</v>
       </c>
       <c r="AO2">
-        <v>5.955928646379854</v>
+        <v>4.469588367806676</v>
       </c>
       <c r="AP2">
-        <v>6.104039940319064</v>
+        <v>5.669910246156581</v>
       </c>
       <c r="AQ2">
-        <v>5.955928646379854</v>
+        <v>4.469588367806676</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0329</v>
+        <v>0.0194</v>
       </c>
       <c r="E3">
-        <v>0.0611</v>
+        <v>0.0549</v>
       </c>
       <c r="F3">
-        <v>0.0785</v>
+        <v>0.106</v>
       </c>
       <c r="G3">
-        <v>0.08484913377733044</v>
+        <v>0.09297391789636097</v>
       </c>
       <c r="H3">
-        <v>0.08484913377733044</v>
+        <v>0.09297391789636097</v>
       </c>
       <c r="I3">
-        <v>0.07292973852710025</v>
+        <v>0.08955977217142951</v>
       </c>
       <c r="J3">
-        <v>0.0549543583857243</v>
+        <v>0.06992661717638164</v>
       </c>
       <c r="K3">
-        <v>1330</v>
+        <v>1524.3</v>
       </c>
       <c r="L3">
-        <v>0.05696297406685654</v>
+        <v>0.06255026837155098</v>
       </c>
       <c r="M3">
-        <v>1224.2</v>
+        <v>1689.6</v>
       </c>
       <c r="N3">
-        <v>0.07701696109517339</v>
+        <v>0.08621991794411217</v>
       </c>
       <c r="O3">
-        <v>0.9204511278195489</v>
+        <v>1.108443219838614</v>
       </c>
       <c r="P3">
-        <v>800.1</v>
+        <v>980</v>
       </c>
       <c r="Q3">
-        <v>0.05033595047561528</v>
+        <v>0.05000918536057643</v>
       </c>
       <c r="R3">
-        <v>0.6015789473684211</v>
+        <v>0.6429180607491963</v>
       </c>
       <c r="S3">
-        <v>424.1</v>
+        <v>709.5999999999999</v>
       </c>
       <c r="T3">
-        <v>0.3464303218428361</v>
+        <v>0.4199810606060606</v>
       </c>
       <c r="U3">
-        <v>6085.6</v>
+        <v>5426.5</v>
       </c>
       <c r="V3">
-        <v>0.3828577180532488</v>
+        <v>0.2769131064889469</v>
       </c>
       <c r="W3">
-        <v>0.07525774362572571</v>
+        <v>0.1352588846000266</v>
       </c>
       <c r="X3">
-        <v>0.1272157391947054</v>
+        <v>0.1029892905569705</v>
       </c>
       <c r="Y3">
-        <v>-0.05195799556897968</v>
+        <v>0.03226959404305607</v>
       </c>
       <c r="Z3">
-        <v>1.92255753633332</v>
+        <v>1.200583314447871</v>
       </c>
       <c r="AA3">
-        <v>0.1056529158688364</v>
+        <v>0.08395272981774771</v>
       </c>
       <c r="AB3">
-        <v>0.08511649710579475</v>
+        <v>0.07432040677157861</v>
       </c>
       <c r="AC3">
-        <v>0.02053641876304167</v>
+        <v>0.009632323046169095</v>
       </c>
       <c r="AD3">
-        <v>16722.5</v>
+        <v>18187.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>16722.5</v>
+        <v>18187.2</v>
       </c>
       <c r="AG3">
-        <v>10636.9</v>
+        <v>12760.7</v>
       </c>
       <c r="AH3">
-        <v>0.5126817648086774</v>
+        <v>0.4813516975619051</v>
       </c>
       <c r="AI3">
-        <v>0.5946898437750047</v>
+        <v>0.655668675914977</v>
       </c>
       <c r="AJ3">
-        <v>0.4009068260710611</v>
+        <v>0.3943709417716668</v>
       </c>
       <c r="AK3">
-        <v>0.4827471963910485</v>
+        <v>0.5719235027048346</v>
       </c>
       <c r="AL3">
-        <v>285.9</v>
+        <v>488.3</v>
       </c>
       <c r="AM3">
-        <v>285.9</v>
+        <v>488.3</v>
       </c>
       <c r="AN3">
-        <v>9.596292895673132</v>
+        <v>8.081045054652094</v>
       </c>
       <c r="AO3">
-        <v>5.955928646379854</v>
+        <v>4.469588367806676</v>
       </c>
       <c r="AP3">
-        <v>6.104039940319064</v>
+        <v>5.669910246156581</v>
       </c>
       <c r="AQ3">
-        <v>5.955928646379854</v>
+        <v>4.469588367806676</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0194</v>
+        <v>-0.13</v>
       </c>
       <c r="E2">
-        <v>0.0549</v>
+        <v>-0.006979999999999999</v>
       </c>
       <c r="F2">
-        <v>0.106</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="G2">
-        <v>0.09297391789636097</v>
+        <v>0.1270383721111683</v>
       </c>
       <c r="H2">
-        <v>0.09297391789636097</v>
+        <v>0.1270383721111683</v>
       </c>
       <c r="I2">
-        <v>0.08955977217142951</v>
+        <v>0.145436387185369</v>
       </c>
       <c r="J2">
-        <v>0.06992661717638164</v>
+        <v>0.1148245377618787</v>
       </c>
       <c r="K2">
-        <v>1524.3</v>
+        <v>1217.4</v>
       </c>
       <c r="L2">
-        <v>0.06255026837155098</v>
+        <v>0.09498618978512242</v>
       </c>
       <c r="M2">
-        <v>1689.6</v>
+        <v>1413.3</v>
       </c>
       <c r="N2">
-        <v>0.08621991794411217</v>
+        <v>0.06531323363587629</v>
       </c>
       <c r="O2">
-        <v>1.108443219838614</v>
+        <v>1.160916707737802</v>
       </c>
       <c r="P2">
-        <v>980</v>
+        <v>1051.6</v>
       </c>
       <c r="Q2">
-        <v>0.05000918536057643</v>
+        <v>0.04859788897720761</v>
       </c>
       <c r="R2">
-        <v>0.6429180607491963</v>
+        <v>0.8638081156563167</v>
       </c>
       <c r="S2">
-        <v>709.5999999999999</v>
+        <v>361.7</v>
       </c>
       <c r="T2">
-        <v>0.4199810606060606</v>
+        <v>0.2559258473077196</v>
       </c>
       <c r="U2">
-        <v>5426.5</v>
+        <v>5803.5</v>
       </c>
       <c r="V2">
-        <v>0.2769131064889469</v>
+        <v>0.2681987910605024</v>
       </c>
       <c r="W2">
-        <v>0.1352588846000266</v>
+        <v>0.1292905692438403</v>
       </c>
       <c r="X2">
-        <v>0.1029892905569705</v>
+        <v>0.1015568563289272</v>
       </c>
       <c r="Y2">
-        <v>0.03226959404305607</v>
+        <v>0.02773371291491306</v>
       </c>
       <c r="Z2">
-        <v>1.200583314447871</v>
+        <v>0.628578995380043</v>
       </c>
       <c r="AA2">
-        <v>0.08395272981774771</v>
+        <v>0.07217629259133951</v>
       </c>
       <c r="AB2">
-        <v>0.07432040677157861</v>
+        <v>0.07801213497339185</v>
       </c>
       <c r="AC2">
-        <v>0.009632323046169095</v>
+        <v>-0.005835842382052342</v>
       </c>
       <c r="AD2">
-        <v>18187.2</v>
+        <v>16549.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>18187.2</v>
+        <v>16549.1</v>
       </c>
       <c r="AG2">
-        <v>12760.7</v>
+        <v>10745.6</v>
       </c>
       <c r="AH2">
-        <v>0.4813516975619051</v>
+        <v>0.4333597815014704</v>
       </c>
       <c r="AI2">
-        <v>0.655668675914977</v>
+        <v>0.656007452332818</v>
       </c>
       <c r="AJ2">
-        <v>0.3943709417716668</v>
+        <v>0.3318140833240696</v>
       </c>
       <c r="AK2">
-        <v>0.5719235027048346</v>
+        <v>0.5532267613972764</v>
       </c>
       <c r="AL2">
-        <v>488.3</v>
+        <v>458.5</v>
       </c>
       <c r="AM2">
-        <v>488.3</v>
+        <v>458.5</v>
       </c>
       <c r="AN2">
-        <v>8.081045054652094</v>
+        <v>8.742722806276083</v>
       </c>
       <c r="AO2">
-        <v>4.469588367806676</v>
+        <v>4.065430752453653</v>
       </c>
       <c r="AP2">
-        <v>5.669910246156581</v>
+        <v>5.676792223572296</v>
       </c>
       <c r="AQ2">
-        <v>4.469588367806676</v>
+        <v>4.065430752453653</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0194</v>
+        <v>-0.13</v>
       </c>
       <c r="E3">
-        <v>0.0549</v>
+        <v>-0.006979999999999999</v>
       </c>
       <c r="F3">
-        <v>0.106</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="G3">
-        <v>0.09297391789636097</v>
+        <v>0.1270383721111683</v>
       </c>
       <c r="H3">
-        <v>0.09297391789636097</v>
+        <v>0.1270383721111683</v>
       </c>
       <c r="I3">
-        <v>0.08955977217142951</v>
+        <v>0.145436387185369</v>
       </c>
       <c r="J3">
-        <v>0.06992661717638164</v>
+        <v>0.1148245377618787</v>
       </c>
       <c r="K3">
-        <v>1524.3</v>
+        <v>1217.4</v>
       </c>
       <c r="L3">
-        <v>0.06255026837155098</v>
+        <v>0.09498618978512242</v>
       </c>
       <c r="M3">
-        <v>1689.6</v>
+        <v>1413.3</v>
       </c>
       <c r="N3">
-        <v>0.08621991794411217</v>
+        <v>0.06531323363587629</v>
       </c>
       <c r="O3">
-        <v>1.108443219838614</v>
+        <v>1.160916707737802</v>
       </c>
       <c r="P3">
-        <v>980</v>
+        <v>1051.6</v>
       </c>
       <c r="Q3">
-        <v>0.05000918536057643</v>
+        <v>0.04859788897720761</v>
       </c>
       <c r="R3">
-        <v>0.6429180607491963</v>
+        <v>0.8638081156563167</v>
       </c>
       <c r="S3">
-        <v>709.5999999999999</v>
+        <v>361.7</v>
       </c>
       <c r="T3">
-        <v>0.4199810606060606</v>
+        <v>0.2559258473077196</v>
       </c>
       <c r="U3">
-        <v>5426.5</v>
+        <v>5803.5</v>
       </c>
       <c r="V3">
-        <v>0.2769131064889469</v>
+        <v>0.2681987910605024</v>
       </c>
       <c r="W3">
-        <v>0.1352588846000266</v>
+        <v>0.1292905692438403</v>
       </c>
       <c r="X3">
-        <v>0.1029892905569705</v>
+        <v>0.1015568563289272</v>
       </c>
       <c r="Y3">
-        <v>0.03226959404305607</v>
+        <v>0.02773371291491306</v>
       </c>
       <c r="Z3">
-        <v>1.200583314447871</v>
+        <v>0.628578995380043</v>
       </c>
       <c r="AA3">
-        <v>0.08395272981774771</v>
+        <v>0.07217629259133951</v>
       </c>
       <c r="AB3">
-        <v>0.07432040677157861</v>
+        <v>0.07801213497339185</v>
       </c>
       <c r="AC3">
-        <v>0.009632323046169095</v>
+        <v>-0.005835842382052342</v>
       </c>
       <c r="AD3">
-        <v>18187.2</v>
+        <v>16549.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>18187.2</v>
+        <v>16549.1</v>
       </c>
       <c r="AG3">
-        <v>12760.7</v>
+        <v>10745.6</v>
       </c>
       <c r="AH3">
-        <v>0.4813516975619051</v>
+        <v>0.4333597815014704</v>
       </c>
       <c r="AI3">
-        <v>0.655668675914977</v>
+        <v>0.656007452332818</v>
       </c>
       <c r="AJ3">
-        <v>0.3943709417716668</v>
+        <v>0.3318140833240696</v>
       </c>
       <c r="AK3">
-        <v>0.5719235027048346</v>
+        <v>0.5532267613972764</v>
       </c>
       <c r="AL3">
-        <v>488.3</v>
+        <v>458.5</v>
       </c>
       <c r="AM3">
-        <v>488.3</v>
+        <v>458.5</v>
       </c>
       <c r="AN3">
-        <v>8.081045054652094</v>
+        <v>8.742722806276083</v>
       </c>
       <c r="AO3">
-        <v>4.469588367806676</v>
+        <v>4.065430752453653</v>
       </c>
       <c r="AP3">
-        <v>5.669910246156581</v>
+        <v>5.676792223572296</v>
       </c>
       <c r="AQ3">
-        <v>4.469588367806676</v>
+        <v>4.065430752453653</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_insurance_life.xlsx
@@ -648,10 +648,10 @@
         <v>0.1292905692438403</v>
       </c>
       <c r="X2">
-        <v>0.1015568563289272</v>
+        <v>0.1015210096276794</v>
       </c>
       <c r="Y2">
-        <v>0.02773371291491306</v>
+        <v>0.02776955961616084</v>
       </c>
       <c r="Z2">
         <v>0.628578995380043</v>
@@ -660,10 +660,10 @@
         <v>0.07217629259133951</v>
       </c>
       <c r="AB2">
-        <v>0.07801213497339185</v>
+        <v>0.07799182279076435</v>
       </c>
       <c r="AC2">
-        <v>-0.005835842382052342</v>
+        <v>-0.005815530199424837</v>
       </c>
       <c r="AD2">
         <v>16549.1</v>
@@ -785,10 +785,10 @@
         <v>0.1292905692438403</v>
       </c>
       <c r="X3">
-        <v>0.1015568563289272</v>
+        <v>0.1015210096276794</v>
       </c>
       <c r="Y3">
-        <v>0.02773371291491306</v>
+        <v>0.02776955961616084</v>
       </c>
       <c r="Z3">
         <v>0.628578995380043</v>
@@ -797,10 +797,10 @@
         <v>0.07217629259133951</v>
       </c>
       <c r="AB3">
-        <v>0.07801213497339185</v>
+        <v>0.07799182279076435</v>
       </c>
       <c r="AC3">
-        <v>-0.005835842382052342</v>
+        <v>-0.005815530199424837</v>
       </c>
       <c r="AD3">
         <v>16549.1</v>
